--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126024174</v>
       </c>
       <c r="B2" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,6 +871,1587 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126217637</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630295</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6665724</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En äldre spillning på en murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126217624</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630385</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665574</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126217627</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6665713</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126217628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90257</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665602</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lila K-reaktion. Kollekt insamlad, dock inte av mig.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126217600</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96596</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665583</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126217649</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91646</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665727</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126217644</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630322</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665785</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Blomning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126217604</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>630393</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6665565</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126217625</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630388</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665623</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126217605</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630388</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665573</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126217647</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91646</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630389</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6665721</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126217646</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91865</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630388</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665591</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126217623</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630416</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6665723</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126217602</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96596</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630379</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665753</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126217642</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91865</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630393</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6665753</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126217626</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91690</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630385</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6665724</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217624</v>
+        <v>126217627</v>
       </c>
       <c r="B5" t="n">
         <v>91690</v>
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630385</v>
+        <v>630397</v>
       </c>
       <c r="R5" t="n">
-        <v>6665574</v>
+        <v>6665713</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217627</v>
+        <v>126217624</v>
       </c>
       <c r="B6" t="n">
         <v>91690</v>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630397</v>
+        <v>630385</v>
       </c>
       <c r="R6" t="n">
-        <v>6665713</v>
+        <v>6665574</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1870,32 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B14" t="n">
-        <v>91646</v>
+        <v>96596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217646</v>
+        <v>126217642</v>
       </c>
       <c r="B15" t="n">
         <v>91865</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630388</v>
+        <v>630393</v>
       </c>
       <c r="R15" t="n">
-        <v>6665591</v>
+        <v>6665753</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2046,6 +2046,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217623</v>
+        <v>126217646</v>
       </c>
       <c r="B16" t="n">
-        <v>91690</v>
+        <v>91865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630416</v>
+        <v>630388</v>
       </c>
       <c r="R16" t="n">
-        <v>6665723</v>
+        <v>6665591</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2143,7 +2144,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217602</v>
+        <v>126217623</v>
       </c>
       <c r="B17" t="n">
-        <v>96596</v>
+        <v>91690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630379</v>
+        <v>630416</v>
       </c>
       <c r="R17" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2241,6 +2241,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2259,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217642</v>
+        <v>126217647</v>
       </c>
       <c r="B18" t="n">
-        <v>91865</v>
+        <v>91646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630393</v>
+        <v>630389</v>
       </c>
       <c r="R18" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2338,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126217627</v>
+        <v>126217624</v>
       </c>
       <c r="B5" t="n">
         <v>91690</v>
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630397</v>
+        <v>630385</v>
       </c>
       <c r="R5" t="n">
-        <v>6665713</v>
+        <v>6665574</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126217624</v>
+        <v>126217627</v>
       </c>
       <c r="B6" t="n">
         <v>91690</v>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630385</v>
+        <v>630397</v>
       </c>
       <c r="R6" t="n">
-        <v>6665574</v>
+        <v>6665713</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -2452,6 +2452,879 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126266852</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>630434</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6665746</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126266846</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>630370</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6665727</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126266855</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98379</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>630391</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6665592</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126266865</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100527</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>630456</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6665710</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126266854</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91534</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>630370</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6665727</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126266845</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>630416</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6665751</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126266853</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>630370</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665727</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126266864</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98262</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>630421</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6665738</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126266842</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>630451</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6665734</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126217624</v>
       </c>
       <c r="B5" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>126217627</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>126217628</v>
       </c>
       <c r="B7" t="n">
-        <v>90257</v>
+        <v>90259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126217600</v>
       </c>
       <c r="B8" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>126217649</v>
       </c>
       <c r="B9" t="n">
-        <v>91646</v>
+        <v>91648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>126217644</v>
       </c>
       <c r="B10" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>126217604</v>
       </c>
       <c r="B11" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>126217625</v>
       </c>
       <c r="B12" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>126217605</v>
       </c>
       <c r="B13" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126217602</v>
       </c>
       <c r="B14" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217642</v>
+        <v>126217647</v>
       </c>
       <c r="B15" t="n">
-        <v>91865</v>
+        <v>91648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630393</v>
+        <v>630389</v>
       </c>
       <c r="R15" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2046,7 +2046,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2068,7 +2067,7 @@
         <v>126217646</v>
       </c>
       <c r="B16" t="n">
-        <v>91865</v>
+        <v>91867</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2164,7 @@
         <v>126217623</v>
       </c>
       <c r="B17" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217647</v>
+        <v>126217642</v>
       </c>
       <c r="B18" t="n">
-        <v>91646</v>
+        <v>91867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4217</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630389</v>
+        <v>630393</v>
       </c>
       <c r="R18" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2339,6 +2338,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>126217626</v>
       </c>
       <c r="B19" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2939,32 +2939,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126266845</v>
+        <v>126266853</v>
       </c>
       <c r="B25" t="n">
-        <v>91238</v>
+        <v>91692</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630416</v>
+        <v>630370</v>
       </c>
       <c r="R25" t="n">
-        <v>6665751</v>
+        <v>6665727</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126266853</v>
+        <v>126266845</v>
       </c>
       <c r="B26" t="n">
-        <v>91692</v>
+        <v>91238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630370</v>
+        <v>630416</v>
       </c>
       <c r="R26" t="n">
-        <v>6665727</v>
+        <v>6665751</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126266864</v>
+        <v>126266842</v>
       </c>
       <c r="B27" t="n">
-        <v>98262</v>
+        <v>96598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630421</v>
+        <v>630451</v>
       </c>
       <c r="R27" t="n">
-        <v>6665738</v>
+        <v>6665734</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3230,32 +3230,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126266842</v>
+        <v>126266864</v>
       </c>
       <c r="B28" t="n">
-        <v>96598</v>
+        <v>98262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630451</v>
+        <v>630421</v>
       </c>
       <c r="R28" t="n">
-        <v>6665734</v>
+        <v>6665738</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1870,32 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126217602</v>
+        <v>126217647</v>
       </c>
       <c r="B14" t="n">
-        <v>96598</v>
+        <v>91648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630379</v>
+        <v>630389</v>
       </c>
       <c r="R14" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217647</v>
+        <v>126217646</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>91867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630389</v>
+        <v>630388</v>
       </c>
       <c r="R15" t="n">
-        <v>6665721</v>
+        <v>6665591</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2064,32 +2064,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217646</v>
+        <v>126217623</v>
       </c>
       <c r="B16" t="n">
-        <v>91867</v>
+        <v>91692</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630388</v>
+        <v>630416</v>
       </c>
       <c r="R16" t="n">
-        <v>6665591</v>
+        <v>6665723</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2143,6 +2143,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2161,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217623</v>
+        <v>126217602</v>
       </c>
       <c r="B17" t="n">
-        <v>91692</v>
+        <v>96598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630416</v>
+        <v>630379</v>
       </c>
       <c r="R17" t="n">
-        <v>6665723</v>
+        <v>6665753</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2240,7 +2241,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126266842</v>
+        <v>126266864</v>
       </c>
       <c r="B27" t="n">
-        <v>96598</v>
+        <v>98262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630451</v>
+        <v>630421</v>
       </c>
       <c r="R27" t="n">
-        <v>6665734</v>
+        <v>6665738</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3230,32 +3230,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126266864</v>
+        <v>126266842</v>
       </c>
       <c r="B28" t="n">
-        <v>98262</v>
+        <v>96598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630421</v>
+        <v>630451</v>
       </c>
       <c r="R28" t="n">
-        <v>6665738</v>
+        <v>6665734</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126024174</v>
       </c>
       <c r="B2" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>126217637</v>
       </c>
       <c r="B4" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126217624</v>
       </c>
       <c r="B5" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>126217627</v>
       </c>
       <c r="B6" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>126217628</v>
       </c>
       <c r="B7" t="n">
-        <v>90259</v>
+        <v>90263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>126217600</v>
       </c>
       <c r="B8" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>126217649</v>
       </c>
       <c r="B9" t="n">
-        <v>91648</v>
+        <v>91652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>126217644</v>
       </c>
       <c r="B10" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>126217604</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>126217625</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>126217605</v>
       </c>
       <c r="B13" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,32 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B14" t="n">
-        <v>91648</v>
+        <v>96602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
@@ -1970,7 +1970,7 @@
         <v>126217646</v>
       </c>
       <c r="B15" t="n">
-        <v>91867</v>
+        <v>91871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,32 +2064,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217623</v>
+        <v>126217642</v>
       </c>
       <c r="B16" t="n">
-        <v>91692</v>
+        <v>91871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630416</v>
+        <v>630393</v>
       </c>
       <c r="R16" t="n">
-        <v>6665723</v>
+        <v>6665753</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217602</v>
+        <v>126217647</v>
       </c>
       <c r="B17" t="n">
-        <v>96598</v>
+        <v>91652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630379</v>
+        <v>630389</v>
       </c>
       <c r="R17" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217642</v>
+        <v>126217623</v>
       </c>
       <c r="B18" t="n">
-        <v>91867</v>
+        <v>91696</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630393</v>
+        <v>630416</v>
       </c>
       <c r="R18" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2360,7 +2360,7 @@
         <v>126217626</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>126266852</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126266846</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>126266855</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126266865</v>
       </c>
       <c r="B23" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>126266854</v>
       </c>
       <c r="B24" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>126266853</v>
       </c>
       <c r="B25" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>126266845</v>
       </c>
       <c r="B26" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126266864</v>
+        <v>126266842</v>
       </c>
       <c r="B27" t="n">
-        <v>98262</v>
+        <v>96602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630421</v>
+        <v>630451</v>
       </c>
       <c r="R27" t="n">
-        <v>6665738</v>
+        <v>6665734</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3230,32 +3230,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126266842</v>
+        <v>126266864</v>
       </c>
       <c r="B28" t="n">
-        <v>96598</v>
+        <v>98266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630451</v>
+        <v>630421</v>
       </c>
       <c r="R28" t="n">
-        <v>6665734</v>
+        <v>6665738</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1286,7 +1286,7 @@
         <v>126217600</v>
       </c>
       <c r="B8" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>126217644</v>
       </c>
       <c r="B10" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,32 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126217602</v>
+        <v>126217646</v>
       </c>
       <c r="B14" t="n">
-        <v>96602</v>
+        <v>91871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630379</v>
+        <v>630388</v>
       </c>
       <c r="R14" t="n">
-        <v>6665753</v>
+        <v>6665591</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217646</v>
+        <v>126217642</v>
       </c>
       <c r="B15" t="n">
         <v>91871</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630388</v>
+        <v>630393</v>
       </c>
       <c r="R15" t="n">
-        <v>6665591</v>
+        <v>6665753</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2046,6 +2046,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217642</v>
+        <v>126217623</v>
       </c>
       <c r="B16" t="n">
-        <v>91871</v>
+        <v>91696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630393</v>
+        <v>630416</v>
       </c>
       <c r="R16" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2162,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B17" t="n">
-        <v>91652</v>
+        <v>96605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R17" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2259,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217623</v>
+        <v>126217647</v>
       </c>
       <c r="B18" t="n">
-        <v>91696</v>
+        <v>91652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630416</v>
+        <v>630389</v>
       </c>
       <c r="R18" t="n">
-        <v>6665723</v>
+        <v>6665721</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2338,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126266846</v>
+        <v>126266855</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>98386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630370</v>
+        <v>630391</v>
       </c>
       <c r="R21" t="n">
-        <v>6665727</v>
+        <v>6665592</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126266855</v>
+        <v>126266846</v>
       </c>
       <c r="B22" t="n">
-        <v>98383</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630391</v>
+        <v>630370</v>
       </c>
       <c r="R22" t="n">
-        <v>6665592</v>
+        <v>6665727</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2748,7 +2748,7 @@
         <v>126266865</v>
       </c>
       <c r="B23" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>126266842</v>
       </c>
       <c r="B27" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>126266864</v>
       </c>
       <c r="B28" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217623</v>
+        <v>126217647</v>
       </c>
       <c r="B16" t="n">
-        <v>91696</v>
+        <v>91652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630416</v>
+        <v>630389</v>
       </c>
       <c r="R16" t="n">
-        <v>6665723</v>
+        <v>6665721</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2144,7 +2144,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217602</v>
+        <v>126217623</v>
       </c>
       <c r="B17" t="n">
-        <v>96605</v>
+        <v>91696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630379</v>
+        <v>630416</v>
       </c>
       <c r="R17" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2242,6 +2241,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B18" t="n">
-        <v>91652</v>
+        <v>96605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R18" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126217600</v>
+        <v>126217649</v>
       </c>
       <c r="B8" t="n">
-        <v>96605</v>
+        <v>91652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630390</v>
+        <v>630421</v>
       </c>
       <c r="R8" t="n">
-        <v>6665583</v>
+        <v>6665727</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1380,32 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126217649</v>
+        <v>126217600</v>
       </c>
       <c r="B9" t="n">
-        <v>91652</v>
+        <v>96605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630421</v>
+        <v>630390</v>
       </c>
       <c r="R9" t="n">
-        <v>6665727</v>
+        <v>6665583</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217642</v>
+        <v>126217623</v>
       </c>
       <c r="B15" t="n">
-        <v>91871</v>
+        <v>91696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630393</v>
+        <v>630416</v>
       </c>
       <c r="R15" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B16" t="n">
-        <v>91652</v>
+        <v>96605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R16" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217623</v>
+        <v>126217642</v>
       </c>
       <c r="B17" t="n">
-        <v>91696</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630416</v>
+        <v>630393</v>
       </c>
       <c r="R17" t="n">
-        <v>6665723</v>
+        <v>6665753</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217602</v>
+        <v>126217647</v>
       </c>
       <c r="B18" t="n">
-        <v>96605</v>
+        <v>91652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630379</v>
+        <v>630389</v>
       </c>
       <c r="R18" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126217649</v>
+        <v>126217600</v>
       </c>
       <c r="B8" t="n">
-        <v>91652</v>
+        <v>96605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630421</v>
+        <v>630390</v>
       </c>
       <c r="R8" t="n">
-        <v>6665727</v>
+        <v>6665583</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1380,32 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126217600</v>
+        <v>126217649</v>
       </c>
       <c r="B9" t="n">
-        <v>96605</v>
+        <v>91652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630390</v>
+        <v>630421</v>
       </c>
       <c r="R9" t="n">
-        <v>6665583</v>
+        <v>6665727</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126024174</v>
       </c>
       <c r="B2" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126024165</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>126217637</v>
       </c>
       <c r="B4" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>126217624</v>
       </c>
       <c r="B5" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>126217627</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>126217628</v>
       </c>
       <c r="B7" t="n">
-        <v>90263</v>
+        <v>90266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126217600</v>
+        <v>126217649</v>
       </c>
       <c r="B8" t="n">
-        <v>96605</v>
+        <v>91655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630390</v>
+        <v>630421</v>
       </c>
       <c r="R8" t="n">
-        <v>6665583</v>
+        <v>6665727</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1380,32 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126217649</v>
+        <v>126217600</v>
       </c>
       <c r="B9" t="n">
-        <v>91652</v>
+        <v>96614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630421</v>
+        <v>630390</v>
       </c>
       <c r="R9" t="n">
-        <v>6665727</v>
+        <v>6665583</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1480,7 +1480,7 @@
         <v>126217644</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>126217604</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>126217625</v>
       </c>
       <c r="B12" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>126217605</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126217646</v>
       </c>
       <c r="B14" t="n">
-        <v>91871</v>
+        <v>91874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>126217623</v>
       </c>
       <c r="B15" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217602</v>
+        <v>126217642</v>
       </c>
       <c r="B16" t="n">
-        <v>96605</v>
+        <v>91874</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630379</v>
+        <v>630393</v>
       </c>
       <c r="R16" t="n">
         <v>6665753</v>
@@ -2144,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2162,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217642</v>
+        <v>126217647</v>
       </c>
       <c r="B17" t="n">
-        <v>91871</v>
+        <v>91655</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>4217</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630393</v>
+        <v>630389</v>
       </c>
       <c r="R17" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2241,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217647</v>
+        <v>126217602</v>
       </c>
       <c r="B18" t="n">
-        <v>91652</v>
+        <v>96614</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630389</v>
+        <v>630379</v>
       </c>
       <c r="R18" t="n">
-        <v>6665721</v>
+        <v>6665753</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2360,7 +2360,7 @@
         <v>126217626</v>
       </c>
       <c r="B19" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>126266852</v>
       </c>
       <c r="B20" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126266855</v>
+        <v>126266846</v>
       </c>
       <c r="B21" t="n">
-        <v>98386</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630391</v>
+        <v>630370</v>
       </c>
       <c r="R21" t="n">
-        <v>6665592</v>
+        <v>6665727</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126266846</v>
+        <v>126266855</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>98395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630370</v>
+        <v>630391</v>
       </c>
       <c r="R22" t="n">
-        <v>6665727</v>
+        <v>6665592</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2748,7 +2748,7 @@
         <v>126266865</v>
       </c>
       <c r="B23" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>126266854</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>126266853</v>
       </c>
       <c r="B25" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>126266845</v>
       </c>
       <c r="B26" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>126266842</v>
       </c>
       <c r="B27" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>126266864</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3325,6 +3325,1267 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126522510</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95810</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>210</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>630521</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6665860</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126522497</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98278</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>630394</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6665762</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126522486</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91265</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>630451</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6665754</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126448702</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>630380</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6665438</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126448701</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>630382</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6665450</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126522514</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98278</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>630401</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6665758</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126522484</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>53</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>630493</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6665880</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126448721</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95857</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>630355</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6665447</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126522509</v>
+      </c>
+      <c r="B37" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>630434</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6665776</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126522483</v>
+      </c>
+      <c r="B38" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>53</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>630440</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6665769</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126522519</v>
+      </c>
+      <c r="B39" t="n">
+        <v>100543</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>630454</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6665718</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126522518</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>630323</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6665732</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126522507</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75014</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>630591</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6665619</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1676,32 +1676,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126217625</v>
+        <v>126217605</v>
       </c>
       <c r="B12" t="n">
-        <v>91699</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
         <v>630388</v>
       </c>
       <c r="R12" t="n">
-        <v>6665623</v>
+        <v>6665573</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -1773,32 +1773,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126217605</v>
+        <v>126217625</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>91699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
         <v>630388</v>
       </c>
       <c r="R13" t="n">
-        <v>6665573</v>
+        <v>6665623</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -1870,32 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126217646</v>
+        <v>126217602</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>96614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630388</v>
+        <v>630379</v>
       </c>
       <c r="R14" t="n">
-        <v>6665591</v>
+        <v>6665753</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217647</v>
+        <v>126217646</v>
       </c>
       <c r="B17" t="n">
-        <v>91655</v>
+        <v>91874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4217</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630389</v>
+        <v>630388</v>
       </c>
       <c r="R17" t="n">
-        <v>6665721</v>
+        <v>6665591</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217602</v>
+        <v>126217647</v>
       </c>
       <c r="B18" t="n">
-        <v>96614</v>
+        <v>91655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630379</v>
+        <v>630389</v>
       </c>
       <c r="R18" t="n">
-        <v>6665753</v>
+        <v>6665721</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126266846</v>
+        <v>126266855</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>98395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630370</v>
+        <v>630391</v>
       </c>
       <c r="R21" t="n">
-        <v>6665727</v>
+        <v>6665592</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126266855</v>
+        <v>126266846</v>
       </c>
       <c r="B22" t="n">
-        <v>98395</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630391</v>
+        <v>630370</v>
       </c>
       <c r="R22" t="n">
-        <v>6665592</v>
+        <v>6665727</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3618,32 +3618,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126448702</v>
+        <v>126522514</v>
       </c>
       <c r="B32" t="n">
-        <v>91699</v>
+        <v>98278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630380</v>
+        <v>630401</v>
       </c>
       <c r="R32" t="n">
-        <v>6665438</v>
+        <v>6665758</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3812,32 +3812,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126522514</v>
+        <v>126448702</v>
       </c>
       <c r="B34" t="n">
-        <v>98278</v>
+        <v>91699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630401</v>
+        <v>630380</v>
       </c>
       <c r="R34" t="n">
-        <v>6665758</v>
+        <v>6665438</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4103,32 +4103,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126522509</v>
+        <v>126522483</v>
       </c>
       <c r="B37" t="n">
-        <v>105396</v>
+        <v>96614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630434</v>
+        <v>630440</v>
       </c>
       <c r="R37" t="n">
-        <v>6665776</v>
+        <v>6665769</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4200,32 +4200,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126522483</v>
+        <v>126522509</v>
       </c>
       <c r="B38" t="n">
-        <v>96614</v>
+        <v>105396</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630440</v>
+        <v>630434</v>
       </c>
       <c r="R38" t="n">
-        <v>6665769</v>
+        <v>6665776</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1283,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126217649</v>
+        <v>126217600</v>
       </c>
       <c r="B8" t="n">
-        <v>91655</v>
+        <v>96614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630421</v>
+        <v>630390</v>
       </c>
       <c r="R8" t="n">
-        <v>6665727</v>
+        <v>6665583</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1380,32 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126217600</v>
+        <v>126217649</v>
       </c>
       <c r="B9" t="n">
-        <v>96614</v>
+        <v>91655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630390</v>
+        <v>630421</v>
       </c>
       <c r="R9" t="n">
-        <v>6665583</v>
+        <v>6665727</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126217605</v>
+        <v>126217625</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>91699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
         <v>630388</v>
       </c>
       <c r="R12" t="n">
-        <v>6665573</v>
+        <v>6665623</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -1773,32 +1773,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126217625</v>
+        <v>126217605</v>
       </c>
       <c r="B13" t="n">
-        <v>91699</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
         <v>630388</v>
       </c>
       <c r="R13" t="n">
-        <v>6665623</v>
+        <v>6665573</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126266855</v>
+        <v>126266846</v>
       </c>
       <c r="B21" t="n">
-        <v>98395</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630391</v>
+        <v>630370</v>
       </c>
       <c r="R21" t="n">
-        <v>6665592</v>
+        <v>6665727</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126266846</v>
+        <v>126266855</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>98395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630370</v>
+        <v>630391</v>
       </c>
       <c r="R22" t="n">
-        <v>6665727</v>
+        <v>6665592</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3618,32 +3618,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126522514</v>
+        <v>126448701</v>
       </c>
       <c r="B32" t="n">
-        <v>98278</v>
+        <v>91699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630401</v>
+        <v>630382</v>
       </c>
       <c r="R32" t="n">
-        <v>6665758</v>
+        <v>6665450</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126448701</v>
+        <v>126448702</v>
       </c>
       <c r="B33" t="n">
         <v>91699</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630382</v>
+        <v>630380</v>
       </c>
       <c r="R33" t="n">
-        <v>6665450</v>
+        <v>6665438</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3812,32 +3812,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126448702</v>
+        <v>126522514</v>
       </c>
       <c r="B34" t="n">
-        <v>91699</v>
+        <v>98278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630380</v>
+        <v>630401</v>
       </c>
       <c r="R34" t="n">
-        <v>6665438</v>
+        <v>6665758</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -3618,32 +3618,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126448701</v>
+        <v>126522514</v>
       </c>
       <c r="B32" t="n">
-        <v>91699</v>
+        <v>98278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630382</v>
+        <v>630401</v>
       </c>
       <c r="R32" t="n">
-        <v>6665450</v>
+        <v>6665758</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126448702</v>
+        <v>126448701</v>
       </c>
       <c r="B33" t="n">
         <v>91699</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630380</v>
+        <v>630382</v>
       </c>
       <c r="R33" t="n">
-        <v>6665438</v>
+        <v>6665450</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3812,32 +3812,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126522514</v>
+        <v>126448702</v>
       </c>
       <c r="B34" t="n">
-        <v>98278</v>
+        <v>91699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630401</v>
+        <v>630380</v>
       </c>
       <c r="R34" t="n">
-        <v>6665758</v>
+        <v>6665438</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -1676,32 +1676,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126217625</v>
+        <v>126217605</v>
       </c>
       <c r="B12" t="n">
-        <v>91699</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
         <v>630388</v>
       </c>
       <c r="R12" t="n">
-        <v>6665623</v>
+        <v>6665573</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -1773,32 +1773,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126217605</v>
+        <v>126217625</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>91699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
         <v>630388</v>
       </c>
       <c r="R13" t="n">
-        <v>6665573</v>
+        <v>6665623</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126217623</v>
+        <v>126217647</v>
       </c>
       <c r="B15" t="n">
-        <v>91699</v>
+        <v>91655</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630416</v>
+        <v>630389</v>
       </c>
       <c r="R15" t="n">
-        <v>6665723</v>
+        <v>6665721</v>
       </c>
       <c r="S15" t="n">
         <v>12</v>
@@ -2046,7 +2046,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2065,32 +2064,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126217642</v>
+        <v>126217623</v>
       </c>
       <c r="B16" t="n">
-        <v>91874</v>
+        <v>91699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630393</v>
+        <v>630416</v>
       </c>
       <c r="R16" t="n">
-        <v>6665753</v>
+        <v>6665723</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2163,7 +2162,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126217646</v>
+        <v>126217642</v>
       </c>
       <c r="B17" t="n">
         <v>91874</v>
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630388</v>
+        <v>630393</v>
       </c>
       <c r="R17" t="n">
-        <v>6665591</v>
+        <v>6665753</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2242,6 +2241,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126217647</v>
+        <v>126217646</v>
       </c>
       <c r="B18" t="n">
-        <v>91655</v>
+        <v>91874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4217</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630389</v>
+        <v>630388</v>
       </c>
       <c r="R18" t="n">
-        <v>6665721</v>
+        <v>6665591</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126266846</v>
+        <v>126266855</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>98395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630370</v>
+        <v>630391</v>
       </c>
       <c r="R21" t="n">
-        <v>6665727</v>
+        <v>6665592</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126266855</v>
+        <v>126266846</v>
       </c>
       <c r="B22" t="n">
-        <v>98395</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630391</v>
+        <v>630370</v>
       </c>
       <c r="R22" t="n">
-        <v>6665592</v>
+        <v>6665727</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3133,32 +3133,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126266842</v>
+        <v>126266864</v>
       </c>
       <c r="B27" t="n">
-        <v>96614</v>
+        <v>98278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630451</v>
+        <v>630421</v>
       </c>
       <c r="R27" t="n">
-        <v>6665734</v>
+        <v>6665738</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3230,32 +3230,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126266864</v>
+        <v>126266842</v>
       </c>
       <c r="B28" t="n">
-        <v>98278</v>
+        <v>96614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630421</v>
+        <v>630451</v>
       </c>
       <c r="R28" t="n">
-        <v>6665738</v>
+        <v>6665734</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -4591,7 +4591,7 @@
         <v>126448703</v>
       </c>
       <c r="B42" t="n">
-        <v>91867</v>
+        <v>91941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101447</v>
+        <v>101522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>91973</v>
+        <v>92047</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -4591,7 +4591,7 @@
         <v>126448703</v>
       </c>
       <c r="B42" t="n">
-        <v>91941</v>
+        <v>91947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101522</v>
+        <v>101528</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>92047</v>
+        <v>92053</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -4591,7 +4591,7 @@
         <v>126448703</v>
       </c>
       <c r="B42" t="n">
-        <v>91947</v>
+        <v>91948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4591,7 +4591,7 @@
         <v>126448703</v>
       </c>
       <c r="B42" t="n">
-        <v>91948</v>
+        <v>91952</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101529</v>
+        <v>101533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>92054</v>
+        <v>92058</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5171,6 +5171,588 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127575465</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>630380</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6665786</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127575455</v>
+      </c>
+      <c r="B49" t="n">
+        <v>95943</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>630479</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6665782</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127575469</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100629</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>630442</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6665735</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127575457</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>353</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>630339</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6665824</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127575432</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>630439</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6665731</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127575462</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>630530</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6665720</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101533</v>
+        <v>101534</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5754,6 +5754,1877 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127704837</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>630401</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6665690</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127704806</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>630361</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6665666</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127704803</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>630387</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6665672</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127704829</v>
+      </c>
+      <c r="B57" t="n">
+        <v>75080</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>630372</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6665685</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127704828</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>630363</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6665674</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Mer än 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127704839</v>
+      </c>
+      <c r="B59" t="n">
+        <v>100630</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>630486</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6665672</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127704802</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>630407</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6665646</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127704838</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>630341</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6665506</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127704841</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100630</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>630370</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6665503</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127704810</v>
+      </c>
+      <c r="B63" t="n">
+        <v>96700</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>630407</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6665656</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127704813</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>630493</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6665671</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127704821</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80025</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>630559</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6665841</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127704805</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>630357</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6665655</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127704831</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95896</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>210</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>630356</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6665454</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127704842</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92000</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>898</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>630362</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6665470</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127704814</v>
+      </c>
+      <c r="B69" t="n">
+        <v>100537</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>630361</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6665666</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127704830</v>
+      </c>
+      <c r="B70" t="n">
+        <v>105486</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>630468</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6665823</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127704840</v>
+      </c>
+      <c r="B71" t="n">
+        <v>100630</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>630357</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6665655</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127704836</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91959</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>630501</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6665652</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -4591,7 +4591,7 @@
         <v>126448703</v>
       </c>
       <c r="B42" t="n">
-        <v>91952</v>
+        <v>91954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>92058</v>
+        <v>92060</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95943</v>
+        <v>95945</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>127575457</v>
       </c>
       <c r="B51" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>127575432</v>
       </c>
       <c r="B52" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>127704829</v>
       </c>
       <c r="B57" t="n">
-        <v>75080</v>
+        <v>75082</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95896</v>
+        <v>95898</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92000</v>
+        <v>92002</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100537</v>
+        <v>100539</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>100632</v>
+        <v>101536</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R59" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R60" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R59" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>100632</v>
+        <v>101536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R60" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7136,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127704842</v>
+        <v>127704814</v>
       </c>
       <c r="B68" t="n">
-        <v>92002</v>
+        <v>100539</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>898</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630362</v>
+        <v>630361</v>
       </c>
       <c r="R68" t="n">
-        <v>6665470</v>
+        <v>6665666</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7215,6 +7215,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7233,32 +7234,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127704814</v>
+        <v>127704842</v>
       </c>
       <c r="B69" t="n">
-        <v>100539</v>
+        <v>92002</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222771</v>
+        <v>898</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7268,10 +7269,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630361</v>
+        <v>630362</v>
       </c>
       <c r="R69" t="n">
-        <v>6665666</v>
+        <v>6665470</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7312,7 +7313,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -4692,7 +4692,7 @@
         <v>127021119</v>
       </c>
       <c r="B43" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127021123</v>
       </c>
       <c r="B44" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127021126</v>
       </c>
       <c r="B45" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>127021147</v>
       </c>
       <c r="B46" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>127021136</v>
       </c>
       <c r="B47" t="n">
-        <v>92060</v>
+        <v>92066</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95945</v>
+        <v>95951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95898</v>
+        <v>95904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7136,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127704814</v>
+        <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>100539</v>
+        <v>92008</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>898</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630361</v>
+        <v>630362</v>
       </c>
       <c r="R68" t="n">
-        <v>6665666</v>
+        <v>6665470</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7215,7 +7215,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7234,32 +7233,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127704842</v>
+        <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>92002</v>
+        <v>100545</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>898</v>
+        <v>222771</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7269,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630362</v>
+        <v>630361</v>
       </c>
       <c r="R69" t="n">
-        <v>6665470</v>
+        <v>6665666</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7313,6 +7312,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95951</v>
+        <v>95954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>127575457</v>
       </c>
       <c r="B51" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>127575432</v>
       </c>
       <c r="B52" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>127704829</v>
       </c>
       <c r="B57" t="n">
-        <v>75082</v>
+        <v>75085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>100638</v>
+        <v>101545</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R59" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>101542</v>
+        <v>100641</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R60" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B61" t="n">
-        <v>91967</v>
+        <v>100641</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R61" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B62" t="n">
-        <v>100638</v>
+        <v>91970</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R62" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127704810</v>
+        <v>127704813</v>
       </c>
       <c r="B63" t="n">
-        <v>96708</v>
+        <v>91341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,21 +6645,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630407</v>
+        <v>630493</v>
       </c>
       <c r="R63" t="n">
-        <v>6665656</v>
+        <v>6665671</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127704813</v>
+        <v>127704810</v>
       </c>
       <c r="B64" t="n">
-        <v>91338</v>
+        <v>96711</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,21 +6742,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630493</v>
+        <v>630407</v>
       </c>
       <c r="R64" t="n">
-        <v>6665671</v>
+        <v>6665656</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6831,7 +6831,7 @@
         <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95904</v>
+        <v>95907</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92008</v>
+        <v>92011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>127575457</v>
       </c>
       <c r="B51" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>127575432</v>
       </c>
       <c r="B52" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704837</v>
+        <v>127704806</v>
       </c>
       <c r="B54" t="n">
-        <v>91970</v>
+        <v>101553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630401</v>
+        <v>630361</v>
       </c>
       <c r="R54" t="n">
-        <v>6665690</v>
+        <v>6665666</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704806</v>
+        <v>127704803</v>
       </c>
       <c r="B55" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630361</v>
+        <v>630387</v>
       </c>
       <c r="R55" t="n">
-        <v>6665666</v>
+        <v>6665672</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704803</v>
+        <v>127704837</v>
       </c>
       <c r="B56" t="n">
-        <v>101545</v>
+        <v>91978</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630387</v>
+        <v>630401</v>
       </c>
       <c r="R56" t="n">
-        <v>6665672</v>
+        <v>6665690</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6050,7 +6050,7 @@
         <v>127704829</v>
       </c>
       <c r="B57" t="n">
-        <v>75085</v>
+        <v>75091</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>127704841</v>
       </c>
       <c r="B61" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>127704838</v>
       </c>
       <c r="B62" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127704813</v>
+        <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>91341</v>
+        <v>96719</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,21 +6645,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630493</v>
+        <v>630407</v>
       </c>
       <c r="R63" t="n">
-        <v>6665671</v>
+        <v>6665656</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127704810</v>
+        <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>96711</v>
+        <v>91349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,21 +6742,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630407</v>
+        <v>630493</v>
       </c>
       <c r="R64" t="n">
-        <v>6665656</v>
+        <v>6665671</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6831,7 +6831,7 @@
         <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95907</v>
+        <v>95915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92011</v>
+        <v>92019</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95962</v>
+        <v>95963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704806</v>
+        <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>101553</v>
+        <v>91979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630361</v>
+        <v>630401</v>
       </c>
       <c r="R54" t="n">
-        <v>6665666</v>
+        <v>6665690</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704803</v>
+        <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630387</v>
+        <v>630361</v>
       </c>
       <c r="R55" t="n">
-        <v>6665672</v>
+        <v>6665666</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704837</v>
+        <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>91978</v>
+        <v>101554</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630401</v>
+        <v>630387</v>
       </c>
       <c r="R56" t="n">
-        <v>6665690</v>
+        <v>6665672</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>101553</v>
+        <v>100650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R59" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>100649</v>
+        <v>101554</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R60" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>100649</v>
+        <v>91979</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R61" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>91978</v>
+        <v>100650</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R62" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127704810</v>
+        <v>127704813</v>
       </c>
       <c r="B63" t="n">
-        <v>96719</v>
+        <v>91350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,21 +6645,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630407</v>
+        <v>630493</v>
       </c>
       <c r="R63" t="n">
-        <v>6665656</v>
+        <v>6665671</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127704813</v>
+        <v>127704810</v>
       </c>
       <c r="B64" t="n">
-        <v>91349</v>
+        <v>96720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,21 +6742,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630493</v>
+        <v>630407</v>
       </c>
       <c r="R64" t="n">
-        <v>6665671</v>
+        <v>6665656</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95915</v>
+        <v>95916</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7136,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127704842</v>
+        <v>127704814</v>
       </c>
       <c r="B68" t="n">
-        <v>92019</v>
+        <v>100557</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>898</v>
+        <v>222771</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630362</v>
+        <v>630361</v>
       </c>
       <c r="R68" t="n">
-        <v>6665470</v>
+        <v>6665666</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7215,6 +7215,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7233,32 +7234,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127704814</v>
+        <v>127704842</v>
       </c>
       <c r="B69" t="n">
-        <v>100556</v>
+        <v>92020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222771</v>
+        <v>898</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7268,10 +7269,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630361</v>
+        <v>630362</v>
       </c>
       <c r="R69" t="n">
-        <v>6665666</v>
+        <v>6665470</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7312,7 +7313,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>100650</v>
+        <v>101554</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R59" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>101554</v>
+        <v>100650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R60" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127704813</v>
+        <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>91350</v>
+        <v>96720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,21 +6645,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630493</v>
+        <v>630407</v>
       </c>
       <c r="R63" t="n">
-        <v>6665671</v>
+        <v>6665656</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127704810</v>
+        <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>96720</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,21 +6742,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>630407</v>
+        <v>630493</v>
       </c>
       <c r="R64" t="n">
-        <v>6665656</v>
+        <v>6665671</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127704821</v>
+        <v>127704805</v>
       </c>
       <c r="B65" t="n">
-        <v>80036</v>
+        <v>101554</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630559</v>
+        <v>630357</v>
       </c>
       <c r="R65" t="n">
-        <v>6665841</v>
+        <v>6665655</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127704805</v>
+        <v>127704821</v>
       </c>
       <c r="B66" t="n">
-        <v>101554</v>
+        <v>80036</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630357</v>
+        <v>630559</v>
       </c>
       <c r="R66" t="n">
-        <v>6665655</v>
+        <v>6665841</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7136,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127704814</v>
+        <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>100557</v>
+        <v>92020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222771</v>
+        <v>898</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630361</v>
+        <v>630362</v>
       </c>
       <c r="R68" t="n">
-        <v>6665666</v>
+        <v>6665470</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7215,7 +7215,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7234,32 +7233,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127704842</v>
+        <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>92020</v>
+        <v>100557</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>898</v>
+        <v>222771</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7269,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630362</v>
+        <v>630361</v>
       </c>
       <c r="R69" t="n">
-        <v>6665470</v>
+        <v>6665666</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7313,6 +7312,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95963</v>
+        <v>95964</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127704805</v>
+        <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>101554</v>
+        <v>80036</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630357</v>
+        <v>630559</v>
       </c>
       <c r="R65" t="n">
-        <v>6665655</v>
+        <v>6665841</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127704821</v>
+        <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>80036</v>
+        <v>101555</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630559</v>
+        <v>630357</v>
       </c>
       <c r="R66" t="n">
-        <v>6665841</v>
+        <v>6665655</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95916</v>
+        <v>95917</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5177,7 +5177,7 @@
         <v>127575465</v>
       </c>
       <c r="B48" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127575455</v>
       </c>
       <c r="B49" t="n">
-        <v>95964</v>
+        <v>95965</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>127575469</v>
       </c>
       <c r="B50" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>127575462</v>
       </c>
       <c r="B53" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704837</v>
+        <v>127704806</v>
       </c>
       <c r="B54" t="n">
-        <v>91980</v>
+        <v>101556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630401</v>
+        <v>630361</v>
       </c>
       <c r="R54" t="n">
-        <v>6665690</v>
+        <v>6665666</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704806</v>
+        <v>127704803</v>
       </c>
       <c r="B55" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630361</v>
+        <v>630387</v>
       </c>
       <c r="R55" t="n">
-        <v>6665666</v>
+        <v>6665672</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704803</v>
+        <v>127704837</v>
       </c>
       <c r="B56" t="n">
-        <v>101555</v>
+        <v>91981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630387</v>
+        <v>630401</v>
       </c>
       <c r="R56" t="n">
-        <v>6665672</v>
+        <v>6665690</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>101555</v>
+        <v>100652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R59" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>100651</v>
+        <v>101556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R60" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B61" t="n">
-        <v>91980</v>
+        <v>100652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R61" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B62" t="n">
-        <v>100651</v>
+        <v>91981</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R62" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95917</v>
+        <v>95918</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92021</v>
+        <v>92022</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>100652</v>
+        <v>91981</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R61" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>91981</v>
+        <v>100652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R62" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127704821</v>
+        <v>127704805</v>
       </c>
       <c r="B65" t="n">
-        <v>80036</v>
+        <v>101556</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>221235</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630559</v>
+        <v>630357</v>
       </c>
       <c r="R65" t="n">
-        <v>6665841</v>
+        <v>6665655</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127704805</v>
+        <v>127704821</v>
       </c>
       <c r="B66" t="n">
-        <v>101556</v>
+        <v>80036</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630357</v>
+        <v>630559</v>
       </c>
       <c r="R66" t="n">
-        <v>6665655</v>
+        <v>6665841</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704806</v>
+        <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>101556</v>
+        <v>91981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630361</v>
+        <v>630401</v>
       </c>
       <c r="R54" t="n">
-        <v>6665666</v>
+        <v>6665690</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704803</v>
+        <v>127704806</v>
       </c>
       <c r="B55" t="n">
         <v>101556</v>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630387</v>
+        <v>630361</v>
       </c>
       <c r="R55" t="n">
-        <v>6665672</v>
+        <v>6665666</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704837</v>
+        <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>91981</v>
+        <v>101556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630401</v>
+        <v>630387</v>
       </c>
       <c r="R56" t="n">
-        <v>6665690</v>
+        <v>6665672</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704837</v>
+        <v>127704806</v>
       </c>
       <c r="B54" t="n">
-        <v>91981</v>
+        <v>101556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630401</v>
+        <v>630361</v>
       </c>
       <c r="R54" t="n">
-        <v>6665690</v>
+        <v>6665666</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704806</v>
+        <v>127704803</v>
       </c>
       <c r="B55" t="n">
         <v>101556</v>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630361</v>
+        <v>630387</v>
       </c>
       <c r="R55" t="n">
-        <v>6665666</v>
+        <v>6665672</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704803</v>
+        <v>127704837</v>
       </c>
       <c r="B56" t="n">
-        <v>101556</v>
+        <v>91981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630387</v>
+        <v>630401</v>
       </c>
       <c r="R56" t="n">
-        <v>6665672</v>
+        <v>6665690</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704806</v>
+        <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>101556</v>
+        <v>91981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630361</v>
+        <v>630401</v>
       </c>
       <c r="R54" t="n">
-        <v>6665666</v>
+        <v>6665690</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704803</v>
+        <v>127704806</v>
       </c>
       <c r="B55" t="n">
         <v>101556</v>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630387</v>
+        <v>630361</v>
       </c>
       <c r="R55" t="n">
-        <v>6665672</v>
+        <v>6665666</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704837</v>
+        <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>91981</v>
+        <v>101556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630401</v>
+        <v>630387</v>
       </c>
       <c r="R56" t="n">
-        <v>6665690</v>
+        <v>6665672</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>100652</v>
+        <v>101556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R59" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>101556</v>
+        <v>100652</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R60" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704837</v>
+        <v>127704806</v>
       </c>
       <c r="B54" t="n">
-        <v>91981</v>
+        <v>101564</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630401</v>
+        <v>630361</v>
       </c>
       <c r="R54" t="n">
-        <v>6665690</v>
+        <v>6665666</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704806</v>
+        <v>127704803</v>
       </c>
       <c r="B55" t="n">
-        <v>101556</v>
+        <v>101564</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630361</v>
+        <v>630387</v>
       </c>
       <c r="R55" t="n">
-        <v>6665666</v>
+        <v>6665672</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704803</v>
+        <v>127704837</v>
       </c>
       <c r="B56" t="n">
-        <v>101556</v>
+        <v>91989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630387</v>
+        <v>630401</v>
       </c>
       <c r="R56" t="n">
-        <v>6665672</v>
+        <v>6665690</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6050,7 +6050,7 @@
         <v>127704829</v>
       </c>
       <c r="B57" t="n">
-        <v>75091</v>
+        <v>75094</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B59" t="n">
-        <v>101556</v>
+        <v>100660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R59" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B60" t="n">
-        <v>100652</v>
+        <v>101564</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R60" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B61" t="n">
-        <v>91981</v>
+        <v>100660</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R61" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B62" t="n">
-        <v>100652</v>
+        <v>91989</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R62" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127704805</v>
+        <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>101556</v>
+        <v>80039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6839,21 +6839,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>630357</v>
+        <v>630559</v>
       </c>
       <c r="R65" t="n">
-        <v>6665655</v>
+        <v>6665841</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127704821</v>
+        <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>80036</v>
+        <v>101564</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>630559</v>
+        <v>630357</v>
       </c>
       <c r="R66" t="n">
-        <v>6665841</v>
+        <v>6665655</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95918</v>
+        <v>95926</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92022</v>
+        <v>92030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91981</v>
+        <v>91989</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -6246,10 +6246,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127704839</v>
+        <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>100660</v>
+        <v>101564</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6257,21 +6257,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630486</v>
+        <v>630407</v>
       </c>
       <c r="R59" t="n">
-        <v>6665672</v>
+        <v>6665646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127704802</v>
+        <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>101564</v>
+        <v>100660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6354,21 +6354,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>630407</v>
+        <v>630486</v>
       </c>
       <c r="R60" t="n">
-        <v>6665646</v>
+        <v>6665672</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6440,10 +6440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127704841</v>
+        <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>100660</v>
+        <v>91989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,21 +6451,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>630370</v>
+        <v>630341</v>
       </c>
       <c r="R61" t="n">
-        <v>6665503</v>
+        <v>6665506</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6537,10 +6537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127704838</v>
+        <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>91989</v>
+        <v>100660</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630341</v>
+        <v>630370</v>
       </c>
       <c r="R62" t="n">
-        <v>6665506</v>
+        <v>6665503</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,10 +5756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127704806</v>
+        <v>127704837</v>
       </c>
       <c r="B54" t="n">
-        <v>101564</v>
+        <v>92000</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5767,21 +5767,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630361</v>
+        <v>630401</v>
       </c>
       <c r="R54" t="n">
-        <v>6665666</v>
+        <v>6665690</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5853,10 +5853,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127704803</v>
+        <v>127704806</v>
       </c>
       <c r="B55" t="n">
-        <v>101564</v>
+        <v>101576</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630387</v>
+        <v>630361</v>
       </c>
       <c r="R55" t="n">
-        <v>6665672</v>
+        <v>6665666</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127704837</v>
+        <v>127704803</v>
       </c>
       <c r="B56" t="n">
-        <v>91989</v>
+        <v>101576</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5961,21 +5961,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630401</v>
+        <v>630387</v>
       </c>
       <c r="R56" t="n">
-        <v>6665690</v>
+        <v>6665672</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6050,7 +6050,7 @@
         <v>127704829</v>
       </c>
       <c r="B57" t="n">
-        <v>75094</v>
+        <v>75105</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>127704828</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>127704802</v>
       </c>
       <c r="B59" t="n">
-        <v>101564</v>
+        <v>101576</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>127704839</v>
       </c>
       <c r="B60" t="n">
-        <v>100660</v>
+        <v>100672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>127704838</v>
       </c>
       <c r="B61" t="n">
-        <v>91989</v>
+        <v>92000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>127704841</v>
       </c>
       <c r="B62" t="n">
-        <v>100660</v>
+        <v>100672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>127704810</v>
       </c>
       <c r="B63" t="n">
-        <v>96730</v>
+        <v>96742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>127704813</v>
       </c>
       <c r="B64" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>127704821</v>
       </c>
       <c r="B65" t="n">
-        <v>80039</v>
+        <v>80050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>127704805</v>
       </c>
       <c r="B66" t="n">
-        <v>101564</v>
+        <v>101576</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>127704831</v>
       </c>
       <c r="B67" t="n">
-        <v>95926</v>
+        <v>95938</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>127704842</v>
       </c>
       <c r="B68" t="n">
-        <v>92030</v>
+        <v>92041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>127704814</v>
       </c>
       <c r="B69" t="n">
-        <v>100567</v>
+        <v>100579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127704830</v>
       </c>
       <c r="B70" t="n">
-        <v>105516</v>
+        <v>105528</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>127704840</v>
       </c>
       <c r="B71" t="n">
-        <v>100660</v>
+        <v>100672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>127704836</v>
       </c>
       <c r="B72" t="n">
-        <v>91989</v>
+        <v>92000</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,6 +7624,5702 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128493971</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>630372</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6665456</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128493973</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>630417</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6665602</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128493970</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>630411</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6665608</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128493972</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>630331</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6665773</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128600686</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>630375</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6665445</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128600676</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91664</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>630389</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6665471</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128600688</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>630366</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6665739</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>precis intill körspåret</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128600682</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>630392</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6665464</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128603997</v>
+      </c>
+      <c r="B81" t="n">
+        <v>105609</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>630460</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6665764</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128603990</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>658</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>630386</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6665464</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128590063</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>630362</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6665582</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128589967</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>630371</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6665591</v>
+      </c>
+      <c r="S84" t="n">
+        <v>12</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128593086</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>630390</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6665765</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128603994</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>630430</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6665725</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128589518</v>
+      </c>
+      <c r="B87" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>630368</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6665479</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128600687</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>630289</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6665724</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128588538</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>630378</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6665440</v>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128603993</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>630298</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6665735</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128600698</v>
+      </c>
+      <c r="B91" t="n">
+        <v>100753</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>630439</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6665715</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128588925</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92074</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>483</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rostskinn</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Crustoderma dryinum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>630378</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6665440</v>
+      </c>
+      <c r="S92" t="n">
+        <v>7</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Lindholm, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128590001</v>
+      </c>
+      <c r="B93" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>630356</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6665573</v>
+      </c>
+      <c r="S93" t="n">
+        <v>11</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128600683</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>658</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>630377</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6665440</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128603989</v>
+      </c>
+      <c r="B95" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>630240</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6665737</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128593271</v>
+      </c>
+      <c r="B96" t="n">
+        <v>96823</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>53</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>630377</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6665750</v>
+      </c>
+      <c r="S96" t="n">
+        <v>3</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128592612</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>630464</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6665720</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128600694</v>
+      </c>
+      <c r="B98" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>630376</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6665474</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128603998</v>
+      </c>
+      <c r="B99" t="n">
+        <v>96019</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>210</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>630377</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6665447</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128587749</v>
+      </c>
+      <c r="B100" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>630394</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6665429</v>
+      </c>
+      <c r="S100" t="n">
+        <v>12</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128604384</v>
+      </c>
+      <c r="B101" t="n">
+        <v>96019</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>210</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>630378</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6665451</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128600685</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>630477</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6665766</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128589263</v>
+      </c>
+      <c r="B103" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>630380</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6665461</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128603992</v>
+      </c>
+      <c r="B104" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>630325</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6665761</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128606124</v>
+      </c>
+      <c r="B105" t="n">
+        <v>86878</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>630265</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6665729</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128592290</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>630420</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6665734</v>
+      </c>
+      <c r="S106" t="n">
+        <v>6</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128606112</v>
+      </c>
+      <c r="B107" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>630311</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6665751</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128592078</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>630423</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6665718</v>
+      </c>
+      <c r="S108" t="n">
+        <v>4</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128593329</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>630355</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6665744</v>
+      </c>
+      <c r="S109" t="n">
+        <v>7</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128600690</v>
+      </c>
+      <c r="B110" t="n">
+        <v>105609</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>630418</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6665720</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128600679</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>112</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>630376</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6665443</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På flera lågor</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128593430</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>630363</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6665752</v>
+      </c>
+      <c r="S112" t="n">
+        <v>7</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128592784</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Karlsro, Karlsro, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>630456</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6665769</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128600693</v>
+      </c>
+      <c r="B114" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>630417</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6665659</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128604784</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>630378</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6665451</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128590073</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>630362</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6665582</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128600689</v>
+      </c>
+      <c r="B117" t="n">
+        <v>105609</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>630429</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6665772</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128602425</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>112</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>630378</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6665439</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Första fyndet i Uppsala kommun!</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Alec Bailey, Anders Lindholm, Beke Regelin, Arvid de Jong, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128601979</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91906</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>630363</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6665738</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128601991</v>
+      </c>
+      <c r="B120" t="n">
+        <v>91673</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>630467</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6665770</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128601993</v>
+      </c>
+      <c r="B121" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>630390</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6665469</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128601982</v>
+      </c>
+      <c r="B122" t="n">
+        <v>90468</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>46</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>630375</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6665763</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128601995</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92122</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>898</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>630383</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6665450</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128601984</v>
+      </c>
+      <c r="B124" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>630350</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6665741</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128601981</v>
+      </c>
+      <c r="B125" t="n">
+        <v>90468</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>46</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>630371</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6665752</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128601983</v>
+      </c>
+      <c r="B126" t="n">
+        <v>90468</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>46</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>630415</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6665628</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128601978</v>
+      </c>
+      <c r="B127" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6665751</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -8031,32 +8031,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128600686</v>
+        <v>128600676</v>
       </c>
       <c r="B77" t="n">
-        <v>97448</v>
+        <v>91664</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>1106</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630375</v>
+        <v>630389</v>
       </c>
       <c r="R77" t="n">
-        <v>6665445</v>
+        <v>6665471</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8128,32 +8128,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128600676</v>
+        <v>128600686</v>
       </c>
       <c r="B78" t="n">
-        <v>91664</v>
+        <v>97448</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1106</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630389</v>
+        <v>630375</v>
       </c>
       <c r="R78" t="n">
-        <v>6665471</v>
+        <v>6665445</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8225,10 +8225,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128600688</v>
+        <v>128600682</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>91906</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8236,38 +8236,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>630366</v>
+        <v>630392</v>
       </c>
       <c r="R79" t="n">
-        <v>6665739</v>
+        <v>6665464</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8300,11 +8296,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>precis intill körspåret</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8331,10 +8322,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128600682</v>
+        <v>128600688</v>
       </c>
       <c r="B80" t="n">
-        <v>91906</v>
+        <v>98571</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8342,34 +8333,38 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630392</v>
+        <v>630366</v>
       </c>
       <c r="R80" t="n">
-        <v>6665464</v>
+        <v>6665739</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8402,6 +8397,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>precis intill körspåret</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9045,57 +9045,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128589518</v>
+        <v>128600687</v>
       </c>
       <c r="B87" t="n">
-        <v>5177</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630368</v>
+        <v>630289</v>
       </c>
       <c r="R87" t="n">
-        <v>6665479</v>
+        <v>6665724</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9133,71 +9128,75 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128600687</v>
+        <v>128589518</v>
       </c>
       <c r="B88" t="n">
-        <v>98571</v>
+        <v>5177</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630289</v>
+        <v>630368</v>
       </c>
       <c r="R88" t="n">
-        <v>6665724</v>
+        <v>6665479</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9235,18 +9234,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9661,57 +9661,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128590001</v>
+        <v>128600683</v>
       </c>
       <c r="B93" t="n">
-        <v>5197</v>
+        <v>91748</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630356</v>
+        <v>630377</v>
       </c>
       <c r="R93" t="n">
-        <v>6665573</v>
+        <v>6665440</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9749,67 +9740,75 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128600683</v>
+        <v>128590001</v>
       </c>
       <c r="B94" t="n">
-        <v>91748</v>
+        <v>5197</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>105930</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>630377</v>
+        <v>630356</v>
       </c>
       <c r="R94" t="n">
-        <v>6665440</v>
+        <v>6665573</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9847,18 +9846,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10059,48 +10059,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128592612</v>
+        <v>128603998</v>
       </c>
       <c r="B97" t="n">
-        <v>91906</v>
+        <v>96019</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>630464</v>
+        <v>630377</v>
       </c>
       <c r="R97" t="n">
-        <v>6665720</v>
+        <v>6665447</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10127,19 +10127,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10154,12 +10144,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10263,48 +10253,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128603998</v>
+        <v>128592612</v>
       </c>
       <c r="B99" t="n">
-        <v>96019</v>
+        <v>91906</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630377</v>
+        <v>630464</v>
       </c>
       <c r="R99" t="n">
-        <v>6665447</v>
+        <v>6665720</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10331,9 +10321,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10348,22 +10348,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128587749</v>
+        <v>128604384</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>96019</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10371,46 +10371,49 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630394</v>
+        <v>630378</v>
       </c>
       <c r="R100" t="n">
-        <v>6665429</v>
+        <v>6665451</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10452,25 +10455,45 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128604384</v>
+        <v>128587749</v>
       </c>
       <c r="B101" t="n">
-        <v>96019</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10478,49 +10501,46 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630378</v>
+        <v>630394</v>
       </c>
       <c r="R101" t="n">
-        <v>6665451</v>
+        <v>6665429</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10562,35 +10582,15 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10694,10 +10694,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128589263</v>
+        <v>128606124</v>
       </c>
       <c r="B103" t="n">
-        <v>5177</v>
+        <v>86878</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,39 +10705,45 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630380</v>
+        <v>630265</v>
       </c>
       <c r="R103" t="n">
-        <v>6665461</v>
+        <v>6665729</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10767,39 +10773,45 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10909,10 +10921,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128606124</v>
+        <v>128589263</v>
       </c>
       <c r="B105" t="n">
-        <v>86878</v>
+        <v>5177</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10920,45 +10932,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630265</v>
+        <v>630380</v>
       </c>
       <c r="R105" t="n">
-        <v>6665729</v>
+        <v>6665461</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10988,93 +10994,98 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128592290</v>
+        <v>128606112</v>
       </c>
       <c r="B106" t="n">
-        <v>91906</v>
+        <v>86944</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>3739</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630420</v>
+        <v>630311</v>
       </c>
       <c r="R106" t="n">
-        <v>6665734</v>
+        <v>6665751</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11101,98 +11112,93 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128606112</v>
+        <v>128592290</v>
       </c>
       <c r="B107" t="n">
-        <v>86944</v>
+        <v>91906</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3739</v>
+        <v>1209</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630311</v>
+        <v>630420</v>
       </c>
       <c r="R107" t="n">
-        <v>6665751</v>
+        <v>6665734</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11219,93 +11225,87 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128592078</v>
+        <v>128600679</v>
       </c>
       <c r="B108" t="n">
-        <v>91906</v>
+        <v>91402</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630423</v>
+        <v>630376</v>
       </c>
       <c r="R108" t="n">
-        <v>6665718</v>
+        <v>6665443</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11332,19 +11332,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:26</t>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På flera lågor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11359,60 +11354,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128593329</v>
+        <v>128600690</v>
       </c>
       <c r="B109" t="n">
-        <v>91906</v>
+        <v>105609</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630355</v>
+        <v>630418</v>
       </c>
       <c r="R109" t="n">
-        <v>6665744</v>
+        <v>6665720</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11439,19 +11434,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11466,60 +11451,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128600690</v>
+        <v>128593329</v>
       </c>
       <c r="B110" t="n">
-        <v>105609</v>
+        <v>91906</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630418</v>
+        <v>630355</v>
       </c>
       <c r="R110" t="n">
-        <v>6665720</v>
+        <v>6665744</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11546,9 +11531,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11563,60 +11558,60 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128600679</v>
+        <v>128592078</v>
       </c>
       <c r="B111" t="n">
-        <v>91402</v>
+        <v>91906</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630376</v>
+        <v>630423</v>
       </c>
       <c r="R111" t="n">
-        <v>6665443</v>
+        <v>6665718</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11643,14 +11638,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På flera lågor</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11665,60 +11665,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128593430</v>
+        <v>128600693</v>
       </c>
       <c r="B112" t="n">
-        <v>91452</v>
+        <v>92081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>630363</v>
+        <v>630417</v>
       </c>
       <c r="R112" t="n">
-        <v>6665752</v>
+        <v>6665659</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11762,22 +11762,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128592784</v>
+        <v>128604784</v>
       </c>
       <c r="B113" t="n">
-        <v>98571</v>
+        <v>91906</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11785,46 +11785,40 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Karlsro, Karlsro, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630456</v>
+        <v>630378</v>
       </c>
       <c r="R113" t="n">
-        <v>6665769</v>
+        <v>6665451</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11862,66 +11856,96 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128600693</v>
+        <v>128592784</v>
       </c>
       <c r="B114" t="n">
-        <v>92081</v>
+        <v>98571</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Karlsro, Karlsro, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630417</v>
+        <v>630456</v>
       </c>
       <c r="R114" t="n">
-        <v>6665659</v>
+        <v>6665769</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11965,63 +11989,60 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128604784</v>
+        <v>128593430</v>
       </c>
       <c r="B115" t="n">
-        <v>91906</v>
+        <v>91452</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>630378</v>
+        <v>630363</v>
       </c>
       <c r="R115" t="n">
-        <v>6665451</v>
+        <v>6665752</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12059,87 +12080,66 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128590073</v>
+        <v>128600689</v>
       </c>
       <c r="B116" t="n">
-        <v>91452</v>
+        <v>105609</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630362</v>
+        <v>630429</v>
       </c>
       <c r="R116" t="n">
-        <v>6665582</v>
+        <v>6665772</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12166,19 +12166,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12193,60 +12183,60 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128600689</v>
+        <v>128590073</v>
       </c>
       <c r="B117" t="n">
-        <v>105609</v>
+        <v>91452</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630429</v>
+        <v>630362</v>
       </c>
       <c r="R117" t="n">
-        <v>6665772</v>
+        <v>6665582</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12273,9 +12263,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12290,12 +12290,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12520,48 +12520,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128601991</v>
+        <v>128601982</v>
       </c>
       <c r="B120" t="n">
-        <v>91673</v>
+        <v>90468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1618</v>
+        <v>46</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rosa jodskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Amylocorticium subincarnatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Peck) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>630467</v>
+        <v>630375</v>
       </c>
       <c r="R120" t="n">
-        <v>6665770</v>
+        <v>6665763</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12601,11 +12598,6 @@
       </c>
       <c r="AE120" t="b">
         <v>0</v>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG120" t="b">
         <v>0</v>
@@ -12722,45 +12714,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128601982</v>
+        <v>128601991</v>
       </c>
       <c r="B122" t="n">
-        <v>90468</v>
+        <v>91673</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>46</v>
+        <v>1618</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosa jodskinn</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Amylocorticium subincarnatum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Peck) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>630375</v>
+        <v>630467</v>
       </c>
       <c r="R122" t="n">
-        <v>6665763</v>
+        <v>6665770</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12800,6 +12795,11 @@
       </c>
       <c r="AE122" t="b">
         <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG122" t="b">
         <v>0</v>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -8622,10 +8622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128590063</v>
+        <v>128603994</v>
       </c>
       <c r="B83" t="n">
-        <v>91906</v>
+        <v>98571</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,34 +8633,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>630362</v>
+        <v>630430</v>
       </c>
       <c r="R83" t="n">
-        <v>6665582</v>
+        <v>6665725</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8690,19 +8690,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:27</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8717,19 +8712,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128589967</v>
+        <v>128590063</v>
       </c>
       <c r="B84" t="n">
         <v>91906</v>
@@ -8760,17 +8755,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630371</v>
+        <v>630362</v>
       </c>
       <c r="R84" t="n">
-        <v>6665591</v>
+        <v>6665582</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8799,7 +8794,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8809,7 +8804,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8824,60 +8819,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128593086</v>
+        <v>128589967</v>
       </c>
       <c r="B85" t="n">
-        <v>92081</v>
+        <v>91906</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630390</v>
+        <v>630371</v>
       </c>
       <c r="R85" t="n">
-        <v>6665765</v>
+        <v>6665591</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8906,7 +8901,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8916,7 +8911,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8931,60 +8926,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128603994</v>
+        <v>128593086</v>
       </c>
       <c r="B86" t="n">
-        <v>98571</v>
+        <v>92081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630430</v>
+        <v>630390</v>
       </c>
       <c r="R86" t="n">
-        <v>6665725</v>
+        <v>6665765</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9011,14 +9006,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9033,64 +9033,69 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128600687</v>
+        <v>128589518</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>5177</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630289</v>
+        <v>630368</v>
       </c>
       <c r="R87" t="n">
-        <v>6665724</v>
+        <v>6665479</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9128,75 +9133,71 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128589518</v>
+        <v>128600687</v>
       </c>
       <c r="B88" t="n">
-        <v>5177</v>
+        <v>98571</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630368</v>
+        <v>630289</v>
       </c>
       <c r="R88" t="n">
-        <v>6665479</v>
+        <v>6665724</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9234,19 +9235,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10059,48 +10059,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128603998</v>
+        <v>128592612</v>
       </c>
       <c r="B97" t="n">
-        <v>96019</v>
+        <v>91906</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>630377</v>
+        <v>630464</v>
       </c>
       <c r="R97" t="n">
-        <v>6665447</v>
+        <v>6665720</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10127,9 +10127,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10144,22 +10154,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128600694</v>
+        <v>128603998</v>
       </c>
       <c r="B98" t="n">
-        <v>92081</v>
+        <v>96019</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10167,37 +10177,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>630376</v>
+        <v>630377</v>
       </c>
       <c r="R98" t="n">
-        <v>6665474</v>
+        <v>6665447</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10241,57 +10251,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128592612</v>
+        <v>128600694</v>
       </c>
       <c r="B99" t="n">
-        <v>91906</v>
+        <v>92081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630464</v>
+        <v>630376</v>
       </c>
       <c r="R99" t="n">
-        <v>6665720</v>
+        <v>6665474</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10321,19 +10331,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10348,12 +10348,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11033,59 +11033,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128606112</v>
+        <v>128592290</v>
       </c>
       <c r="B106" t="n">
-        <v>86944</v>
+        <v>91906</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3739</v>
+        <v>1209</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>630311</v>
+        <v>630420</v>
       </c>
       <c r="R106" t="n">
-        <v>6665751</v>
+        <v>6665734</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11112,93 +11101,98 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128592290</v>
+        <v>128606112</v>
       </c>
       <c r="B107" t="n">
-        <v>91906</v>
+        <v>86944</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1209</v>
+        <v>3739</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>630420</v>
+        <v>630311</v>
       </c>
       <c r="R107" t="n">
-        <v>6665734</v>
+        <v>6665751</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11225,71 +11219,77 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128600679</v>
+        <v>128600690</v>
       </c>
       <c r="B108" t="n">
-        <v>91402</v>
+        <v>105609</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>112</v>
+        <v>221144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630376</v>
+        <v>630418</v>
       </c>
       <c r="R108" t="n">
-        <v>6665443</v>
+        <v>6665720</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11335,11 +11335,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På flera lågor</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11366,32 +11361,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128600690</v>
+        <v>128600679</v>
       </c>
       <c r="B109" t="n">
-        <v>105609</v>
+        <v>91402</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221144</v>
+        <v>112</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11401,10 +11396,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630418</v>
+        <v>630376</v>
       </c>
       <c r="R109" t="n">
-        <v>6665720</v>
+        <v>6665443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11437,6 +11432,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På flera lågor</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,48 +11677,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128600693</v>
+        <v>128593430</v>
       </c>
       <c r="B112" t="n">
-        <v>92081</v>
+        <v>91452</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>630417</v>
+        <v>630363</v>
       </c>
       <c r="R112" t="n">
-        <v>6665659</v>
+        <v>6665752</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11762,22 +11762,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128604784</v>
+        <v>128592784</v>
       </c>
       <c r="B113" t="n">
-        <v>91906</v>
+        <v>98571</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11785,40 +11785,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Karlsro, Karlsro, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630378</v>
+        <v>630456</v>
       </c>
       <c r="R113" t="n">
-        <v>6665451</v>
+        <v>6665769</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11856,96 +11862,66 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128592784</v>
+        <v>128600693</v>
       </c>
       <c r="B114" t="n">
-        <v>98571</v>
+        <v>92081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Karlsro, Karlsro, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630456</v>
+        <v>630417</v>
       </c>
       <c r="R114" t="n">
-        <v>6665769</v>
+        <v>6665659</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11989,60 +11965,63 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128593430</v>
+        <v>128604784</v>
       </c>
       <c r="B115" t="n">
-        <v>91452</v>
+        <v>91906</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>630363</v>
+        <v>630378</v>
       </c>
       <c r="R115" t="n">
-        <v>6665752</v>
+        <v>6665451</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12080,18 +12059,39 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -7630,7 +7630,7 @@
         <v>128493971</v>
       </c>
       <c r="B73" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>128493973</v>
       </c>
       <c r="B74" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>128493970</v>
       </c>
       <c r="B75" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>128493972</v>
       </c>
       <c r="B76" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>128600676</v>
       </c>
       <c r="B77" t="n">
-        <v>91664</v>
+        <v>91670</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>128600686</v>
       </c>
       <c r="B78" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>128600682</v>
       </c>
       <c r="B79" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>128600688</v>
       </c>
       <c r="B80" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>128603997</v>
       </c>
       <c r="B81" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>128603990</v>
       </c>
       <c r="B82" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8622,10 +8622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128603994</v>
+        <v>128590063</v>
       </c>
       <c r="B83" t="n">
-        <v>98571</v>
+        <v>91912</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,34 +8633,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>630430</v>
+        <v>630362</v>
       </c>
       <c r="R83" t="n">
-        <v>6665725</v>
+        <v>6665582</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8690,14 +8690,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8712,22 +8717,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128590063</v>
+        <v>128589967</v>
       </c>
       <c r="B84" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8755,17 +8760,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630362</v>
+        <v>630371</v>
       </c>
       <c r="R84" t="n">
-        <v>6665582</v>
+        <v>6665591</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8794,7 +8799,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8804,7 +8809,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8819,60 +8824,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128589967</v>
+        <v>128593086</v>
       </c>
       <c r="B85" t="n">
-        <v>91906</v>
+        <v>92087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630371</v>
+        <v>630390</v>
       </c>
       <c r="R85" t="n">
-        <v>6665591</v>
+        <v>6665765</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8901,7 +8906,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8911,7 +8916,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8926,60 +8931,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128593086</v>
+        <v>128603994</v>
       </c>
       <c r="B86" t="n">
-        <v>92081</v>
+        <v>98579</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630390</v>
+        <v>630430</v>
       </c>
       <c r="R86" t="n">
-        <v>6665765</v>
+        <v>6665725</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9006,19 +9011,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9033,69 +9033,64 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128589518</v>
+        <v>128600687</v>
       </c>
       <c r="B87" t="n">
-        <v>5177</v>
+        <v>98579</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630368</v>
+        <v>630289</v>
       </c>
       <c r="R87" t="n">
-        <v>6665479</v>
+        <v>6665724</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9133,71 +9128,75 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128600687</v>
+        <v>128589518</v>
       </c>
       <c r="B88" t="n">
-        <v>98571</v>
+        <v>5177</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630289</v>
+        <v>630368</v>
       </c>
       <c r="R88" t="n">
-        <v>6665724</v>
+        <v>6665479</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9235,18 +9234,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
         <v>128588538</v>
       </c>
       <c r="B89" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>128603993</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>128600698</v>
       </c>
       <c r="B91" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>128588925</v>
       </c>
       <c r="B92" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>128600683</v>
       </c>
       <c r="B93" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9865,48 +9865,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128603989</v>
+        <v>128593271</v>
       </c>
       <c r="B95" t="n">
-        <v>92387</v>
+        <v>96829</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630240</v>
+        <v>630377</v>
       </c>
       <c r="R95" t="n">
-        <v>6665737</v>
+        <v>6665750</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9950,60 +9950,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128593271</v>
+        <v>128603989</v>
       </c>
       <c r="B96" t="n">
-        <v>96823</v>
+        <v>92393</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630377</v>
+        <v>630240</v>
       </c>
       <c r="R96" t="n">
-        <v>6665750</v>
+        <v>6665737</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10047,12 +10047,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10062,7 +10062,7 @@
         <v>128592612</v>
       </c>
       <c r="B97" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>128603998</v>
       </c>
       <c r="B98" t="n">
-        <v>96019</v>
+        <v>96025</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>128600694</v>
       </c>
       <c r="B99" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10360,10 +10360,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128604384</v>
+        <v>128587749</v>
       </c>
       <c r="B100" t="n">
-        <v>96019</v>
+        <v>5197</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10371,49 +10371,46 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630378</v>
+        <v>630394</v>
       </c>
       <c r="R100" t="n">
-        <v>6665451</v>
+        <v>6665429</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10455,45 +10452,25 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128587749</v>
+        <v>128604384</v>
       </c>
       <c r="B101" t="n">
-        <v>5197</v>
+        <v>96025</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10501,46 +10478,49 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630394</v>
+        <v>630378</v>
       </c>
       <c r="R101" t="n">
-        <v>6665429</v>
+        <v>6665451</v>
       </c>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10582,15 +10562,35 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10600,7 +10600,7 @@
         <v>128600685</v>
       </c>
       <c r="B102" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>128606124</v>
       </c>
       <c r="B103" t="n">
-        <v>86878</v>
+        <v>86882</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10811,55 +10811,60 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128603992</v>
+        <v>128589263</v>
       </c>
       <c r="B104" t="n">
-        <v>98571</v>
+        <v>5177</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630325</v>
+        <v>630380</v>
       </c>
       <c r="R104" t="n">
-        <v>6665761</v>
+        <v>6665461</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10886,14 +10891,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10902,72 +10912,66 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128589263</v>
+        <v>128603992</v>
       </c>
       <c r="B105" t="n">
-        <v>5177</v>
+        <v>98579</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630380</v>
+        <v>630325</v>
       </c>
       <c r="R105" t="n">
-        <v>6665461</v>
+        <v>6665761</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10994,19 +10998,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>11:04</t>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11015,18 +11014,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11036,7 +11036,7 @@
         <v>128592290</v>
       </c>
       <c r="B106" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128606112</v>
       </c>
       <c r="B107" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11264,48 +11264,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128600690</v>
+        <v>128593329</v>
       </c>
       <c r="B108" t="n">
-        <v>105609</v>
+        <v>91912</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630418</v>
+        <v>630355</v>
       </c>
       <c r="R108" t="n">
-        <v>6665720</v>
+        <v>6665744</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11332,9 +11332,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11349,60 +11359,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128600679</v>
+        <v>128592078</v>
       </c>
       <c r="B109" t="n">
-        <v>91402</v>
+        <v>91912</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>630376</v>
+        <v>630423</v>
       </c>
       <c r="R109" t="n">
-        <v>6665443</v>
+        <v>6665718</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11429,14 +11439,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På flera lågor</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11451,60 +11466,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128593329</v>
+        <v>128600679</v>
       </c>
       <c r="B110" t="n">
-        <v>91906</v>
+        <v>91408</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630355</v>
+        <v>630376</v>
       </c>
       <c r="R110" t="n">
-        <v>6665744</v>
+        <v>6665443</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11531,19 +11546,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På flera lågor</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11558,60 +11568,60 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128592078</v>
+        <v>128600690</v>
       </c>
       <c r="B111" t="n">
-        <v>91906</v>
+        <v>105621</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630423</v>
+        <v>630418</v>
       </c>
       <c r="R111" t="n">
-        <v>6665718</v>
+        <v>6665720</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11638,19 +11648,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11665,12 +11665,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11680,7 +11680,7 @@
         <v>128593430</v>
       </c>
       <c r="B112" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11774,57 +11774,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128592784</v>
+        <v>128600693</v>
       </c>
       <c r="B113" t="n">
-        <v>98571</v>
+        <v>92087</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Karlsro, Karlsro, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630456</v>
+        <v>630417</v>
       </c>
       <c r="R113" t="n">
-        <v>6665769</v>
+        <v>6665659</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11868,57 +11859,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128600693</v>
+        <v>128604784</v>
       </c>
       <c r="B114" t="n">
-        <v>92081</v>
+        <v>91912</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630417</v>
+        <v>630378</v>
       </c>
       <c r="R114" t="n">
-        <v>6665659</v>
+        <v>6665451</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,28 +11953,49 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128604784</v>
+        <v>128592784</v>
       </c>
       <c r="B115" t="n">
-        <v>91906</v>
+        <v>98579</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11988,40 +12003,46 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Karlsro, Karlsro, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>630378</v>
+        <v>630456</v>
       </c>
       <c r="R115" t="n">
-        <v>6665451</v>
+        <v>6665769</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12059,87 +12080,66 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128600689</v>
+        <v>128590073</v>
       </c>
       <c r="B116" t="n">
-        <v>105609</v>
+        <v>91458</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>630429</v>
+        <v>630362</v>
       </c>
       <c r="R116" t="n">
-        <v>6665772</v>
+        <v>6665582</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12166,9 +12166,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12183,60 +12193,60 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128590073</v>
+        <v>128600689</v>
       </c>
       <c r="B117" t="n">
-        <v>91452</v>
+        <v>105621</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>630362</v>
+        <v>630429</v>
       </c>
       <c r="R117" t="n">
-        <v>6665582</v>
+        <v>6665772</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12263,19 +12273,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12290,12 +12290,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12305,7 +12305,7 @@
         <v>128602425</v>
       </c>
       <c r="B118" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>128601979</v>
       </c>
       <c r="B119" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>128601982</v>
       </c>
       <c r="B120" t="n">
-        <v>90468</v>
+        <v>90474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>128601993</v>
       </c>
       <c r="B121" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>128601991</v>
       </c>
       <c r="B122" t="n">
-        <v>91673</v>
+        <v>91679</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>128601995</v>
       </c>
       <c r="B123" t="n">
-        <v>92122</v>
+        <v>92128</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>128601984</v>
       </c>
       <c r="B124" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>128601981</v>
       </c>
       <c r="B125" t="n">
-        <v>90468</v>
+        <v>90474</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>128601983</v>
       </c>
       <c r="B126" t="n">
-        <v>90468</v>
+        <v>90474</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>128601978</v>
       </c>
       <c r="B127" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -7832,7 +7832,7 @@
         <v>128493970</v>
       </c>
       <c r="B75" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>128600676</v>
       </c>
       <c r="B77" t="n">
-        <v>91670</v>
+        <v>91676</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>128600686</v>
       </c>
       <c r="B78" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>128600682</v>
       </c>
       <c r="B79" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>128600688</v>
       </c>
       <c r="B80" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>128603997</v>
       </c>
       <c r="B81" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>128603990</v>
       </c>
       <c r="B82" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8622,10 +8622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128590063</v>
+        <v>128603994</v>
       </c>
       <c r="B83" t="n">
-        <v>91912</v>
+        <v>98585</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,34 +8633,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>630362</v>
+        <v>630430</v>
       </c>
       <c r="R83" t="n">
-        <v>6665582</v>
+        <v>6665725</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8690,19 +8690,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:27</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8717,22 +8712,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128589967</v>
+        <v>128590063</v>
       </c>
       <c r="B84" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8760,17 +8755,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630371</v>
+        <v>630362</v>
       </c>
       <c r="R84" t="n">
-        <v>6665591</v>
+        <v>6665582</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8799,7 +8794,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8809,7 +8804,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8824,60 +8819,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128593086</v>
+        <v>128589967</v>
       </c>
       <c r="B85" t="n">
-        <v>92087</v>
+        <v>91918</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630390</v>
+        <v>630371</v>
       </c>
       <c r="R85" t="n">
-        <v>6665765</v>
+        <v>6665591</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8906,7 +8901,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8916,7 +8911,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8931,60 +8926,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128603994</v>
+        <v>128593086</v>
       </c>
       <c r="B86" t="n">
-        <v>98579</v>
+        <v>92093</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630430</v>
+        <v>630390</v>
       </c>
       <c r="R86" t="n">
-        <v>6665725</v>
+        <v>6665765</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9011,14 +9006,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9033,64 +9033,69 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128600687</v>
+        <v>128589518</v>
       </c>
       <c r="B87" t="n">
-        <v>98579</v>
+        <v>5177</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630289</v>
+        <v>630368</v>
       </c>
       <c r="R87" t="n">
-        <v>6665724</v>
+        <v>6665479</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9128,75 +9133,71 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128589518</v>
+        <v>128600687</v>
       </c>
       <c r="B88" t="n">
-        <v>5177</v>
+        <v>98585</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630368</v>
+        <v>630289</v>
       </c>
       <c r="R88" t="n">
-        <v>6665479</v>
+        <v>6665724</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9234,19 +9235,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
         <v>128588538</v>
       </c>
       <c r="B89" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9360,48 +9360,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128603993</v>
+        <v>128600698</v>
       </c>
       <c r="B90" t="n">
-        <v>98579</v>
+        <v>100768</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630298</v>
+        <v>630439</v>
       </c>
       <c r="R90" t="n">
-        <v>6665735</v>
+        <v>6665715</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9445,60 +9445,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128600698</v>
+        <v>128603993</v>
       </c>
       <c r="B91" t="n">
-        <v>100761</v>
+        <v>98585</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>630439</v>
+        <v>630298</v>
       </c>
       <c r="R91" t="n">
-        <v>6665715</v>
+        <v>6665735</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9542,12 +9542,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9557,7 +9557,7 @@
         <v>128588925</v>
       </c>
       <c r="B92" t="n">
-        <v>92080</v>
+        <v>92086</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>128600683</v>
       </c>
       <c r="B93" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>128593271</v>
       </c>
       <c r="B95" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>128603989</v>
       </c>
       <c r="B96" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10059,48 +10059,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128592612</v>
+        <v>128603998</v>
       </c>
       <c r="B97" t="n">
-        <v>91912</v>
+        <v>96031</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>630464</v>
+        <v>630377</v>
       </c>
       <c r="R97" t="n">
-        <v>6665720</v>
+        <v>6665447</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10127,19 +10127,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10154,60 +10144,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128603998</v>
+        <v>128592612</v>
       </c>
       <c r="B98" t="n">
-        <v>96025</v>
+        <v>91918</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>630377</v>
+        <v>630464</v>
       </c>
       <c r="R98" t="n">
-        <v>6665447</v>
+        <v>6665720</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10234,9 +10224,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10251,12 +10251,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10266,7 +10266,7 @@
         <v>128600694</v>
       </c>
       <c r="B99" t="n">
-        <v>92087</v>
+        <v>92093</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>128604384</v>
       </c>
       <c r="B101" t="n">
-        <v>96025</v>
+        <v>96031</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10600,7 +10600,7 @@
         <v>128600685</v>
       </c>
       <c r="B102" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10694,10 +10694,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128606124</v>
+        <v>128589263</v>
       </c>
       <c r="B103" t="n">
-        <v>86882</v>
+        <v>5177</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10705,45 +10705,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>100526</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630265</v>
+        <v>630380</v>
       </c>
       <c r="R103" t="n">
-        <v>6665729</v>
+        <v>6665461</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10773,98 +10767,87 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128589263</v>
+        <v>128603992</v>
       </c>
       <c r="B104" t="n">
-        <v>5177</v>
+        <v>98585</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630380</v>
+        <v>630325</v>
       </c>
       <c r="R104" t="n">
-        <v>6665461</v>
+        <v>6665761</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10891,19 +10874,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>11:04</t>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10912,66 +10890,78 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128603992</v>
+        <v>128606124</v>
       </c>
       <c r="B105" t="n">
-        <v>98579</v>
+        <v>86888</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630325</v>
+        <v>630265</v>
       </c>
       <c r="R105" t="n">
-        <v>6665761</v>
+        <v>6665729</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11001,11 +10991,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11018,15 +11003,30 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11036,7 +11036,7 @@
         <v>128592290</v>
       </c>
       <c r="B106" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>128606112</v>
       </c>
       <c r="B107" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>128593329</v>
       </c>
       <c r="B108" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>128592078</v>
       </c>
       <c r="B109" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>128600679</v>
       </c>
       <c r="B110" t="n">
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>128600690</v>
       </c>
       <c r="B111" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>128593430</v>
       </c>
       <c r="B112" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11774,45 +11774,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128600693</v>
+        <v>128604784</v>
       </c>
       <c r="B113" t="n">
-        <v>92087</v>
+        <v>91918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>630417</v>
+        <v>630378</v>
       </c>
       <c r="R113" t="n">
-        <v>6665659</v>
+        <v>6665451</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11853,66 +11856,84 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128604784</v>
+        <v>128600693</v>
       </c>
       <c r="B114" t="n">
-        <v>91912</v>
+        <v>92093</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>630378</v>
+        <v>630417</v>
       </c>
       <c r="R114" t="n">
-        <v>6665451</v>
+        <v>6665659</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,39 +11974,18 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -11995,7 +11995,7 @@
         <v>128592784</v>
       </c>
       <c r="B115" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>128590073</v>
       </c>
       <c r="B116" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>128600689</v>
       </c>
       <c r="B117" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>128602425</v>
       </c>
       <c r="B118" t="n">
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>128601979</v>
       </c>
       <c r="B119" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>128601982</v>
       </c>
       <c r="B120" t="n">
-        <v>90474</v>
+        <v>90480</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>128601993</v>
       </c>
       <c r="B121" t="n">
-        <v>92087</v>
+        <v>92093</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>128601991</v>
       </c>
       <c r="B122" t="n">
-        <v>91679</v>
+        <v>91685</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>128601995</v>
       </c>
       <c r="B123" t="n">
-        <v>92128</v>
+        <v>92134</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>128601984</v>
       </c>
       <c r="B124" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>128601981</v>
       </c>
       <c r="B125" t="n">
-        <v>90474</v>
+        <v>90480</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>128601983</v>
       </c>
       <c r="B126" t="n">
-        <v>90474</v>
+        <v>90480</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>128601978</v>
       </c>
       <c r="B127" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 38958-2024 artfynd.xlsx
+++ b/artfynd/A 38958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8031,32 +8031,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128600676</v>
+        <v>128600686</v>
       </c>
       <c r="B77" t="n">
-        <v>91676</v>
+        <v>97460</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1106</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>630389</v>
+        <v>630375</v>
       </c>
       <c r="R77" t="n">
-        <v>6665471</v>
+        <v>6665445</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8128,32 +8128,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128600686</v>
+        <v>128600676</v>
       </c>
       <c r="B78" t="n">
-        <v>97460</v>
+        <v>91676</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>1106</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>630375</v>
+        <v>630389</v>
       </c>
       <c r="R78" t="n">
-        <v>6665445</v>
+        <v>6665471</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8622,10 +8622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128603994</v>
+        <v>128590063</v>
       </c>
       <c r="B83" t="n">
-        <v>98585</v>
+        <v>91918</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,34 +8633,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>630430</v>
+        <v>630362</v>
       </c>
       <c r="R83" t="n">
-        <v>6665725</v>
+        <v>6665582</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8690,14 +8690,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8712,19 +8717,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128590063</v>
+        <v>128589967</v>
       </c>
       <c r="B84" t="n">
         <v>91918</v>
@@ -8755,17 +8760,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Gogubbkärret, Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630362</v>
+        <v>630371</v>
       </c>
       <c r="R84" t="n">
-        <v>6665582</v>
+        <v>6665591</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8794,7 +8799,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8804,7 +8809,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8819,60 +8824,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128589967</v>
+        <v>128593086</v>
       </c>
       <c r="B85" t="n">
-        <v>91918</v>
+        <v>92093</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Gogubbkärret, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630371</v>
+        <v>630390</v>
       </c>
       <c r="R85" t="n">
-        <v>6665591</v>
+        <v>6665765</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8901,7 +8906,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8911,7 +8916,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8926,60 +8931,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128593086</v>
+        <v>128603994</v>
       </c>
       <c r="B86" t="n">
-        <v>92093</v>
+        <v>98585</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630390</v>
+        <v>630430</v>
       </c>
       <c r="R86" t="n">
-        <v>6665765</v>
+        <v>6665725</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9006,19 +9011,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9033,12 +9033,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128587749</v>
+        <v>128604384</v>
       </c>
       <c r="B100" t="n">
-        <v>5197</v>
+        <v>96031</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10371,46 +10371,49 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>630394</v>
+        <v>630378</v>
       </c>
       <c r="R100" t="n">
-        <v>6665429</v>
+        <v>6665451</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10452,25 +10455,45 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128604384</v>
+        <v>128587749</v>
       </c>
       <c r="B101" t="n">
-        <v>96031</v>
+        <v>5197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10478,49 +10501,46 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630378</v>
+        <v>630394</v>
       </c>
       <c r="R101" t="n">
-        <v>6665451</v>
+        <v>6665429</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10562,35 +10582,15 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10806,48 +10806,59 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128603992</v>
+        <v>128606124</v>
       </c>
       <c r="B104" t="n">
-        <v>98585</v>
+        <v>86888</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>630325</v>
+        <v>630265</v>
       </c>
       <c r="R104" t="n">
-        <v>6665761</v>
+        <v>6665729</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10877,11 +10888,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10894,74 +10900,78 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128606124</v>
+        <v>128603992</v>
       </c>
       <c r="B105" t="n">
-        <v>86888</v>
+        <v>98585</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>630265</v>
+        <v>630325</v>
       </c>
       <c r="R105" t="n">
-        <v>6665729</v>
+        <v>6665761</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10991,6 +11001,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ca 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11003,30 +11018,15 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -13321,6 +13321,228 @@
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128590550</v>
+      </c>
+      <c r="B128" t="n">
+        <v>90482</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>46</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>630403</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6665598</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128591240</v>
+      </c>
+      <c r="B129" t="n">
+        <v>90482</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>46</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>630415</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6665629</v>
+      </c>
+      <c r="S129" t="n">
+        <v>7</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
